--- a/nica-apify/calendario/plan-fase1-2026-10-23.xlsx
+++ b/nica-apify/calendario/plan-fase1-2026-10-23.xlsx
@@ -477,7 +477,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A7"/>
+  <dimension ref="A1:A8"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="120" customWidth="1" min="1" max="1"/>
@@ -493,14 +493,14 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>Producto: Activaciones Robóticas Millonarias $500 · LIVE gratis en TikTok martes 27 oct, 10:00 AM y 7:00 PM CDMX.</t>
+          <t>Producto: Activaciones Robóticas Millonarias $500 · LIVE GRATIS por ZOOM (privado, solo para registrados) martes 27 oct, 10:00 AM y 7:00 PM CDMX: «LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO». Registro: formulario de Brevo (nombre, correo, país; botón 1 de linktr.ee/mabradiante y banner en www.mabradiante.com) → comunidad de WhatsApp → link de Zoom por correo y por WhatsApp.</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
         <is>
-          <t>En el LIVE: Robóticas $500 y Pack de Autohipnosis BNQ™ (5 audios) $2,500 solo en el LIVE; después $3,000.</t>
+          <t>Al terminar el LIVE: primero Activaciones Robóticas Millonarias, 1 minuto para salir de la escasez ($500). Venta principal: Pack de Hipnosis BNQ™ (5 audios) a $2,500 solo durante el LIVE (cierra martes 27 a las 21:00 CDMX); después $3,000.</t>
         </is>
       </c>
     </row>
@@ -529,6 +529,13 @@
       <c r="A7" s="2" t="inlineStr">
         <is>
           <t>Nada se publica ni se gasta sin tu OK.</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="2" t="inlineStr">
+        <is>
+          <t>Las piezas de contenido se siguen publicando en TikTok (principal), Reels y Shorts; la sesión de hipnosis del martes 27 es por Zoom. CTA de invitación: «Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp».</t>
         </is>
       </c>
     </row>
@@ -604,12 +611,12 @@
       </c>
       <c r="D2" s="4" t="inlineStr">
         <is>
-          <t>Invitar al LIVE del martes 27 (registro: grupo de WhatsApp)</t>
+          <t>Invitar al LIVE por Zoom del martes 27 (registro: formulario de Brevo → comunidad de WhatsApp → link de Zoom por correo y WhatsApp)</t>
         </is>
       </c>
       <c r="E2" s="4" t="inlineStr">
         <is>
-          <t>Audio robótico diario + invitación al LIVE</t>
+          <t>Audio robótico diario + invitación a registrarse al LIVE</t>
         </is>
       </c>
       <c r="F2" s="4" t="inlineStr">
@@ -636,7 +643,7 @@
       </c>
       <c r="D3" s="4" t="inlineStr">
         <is>
-          <t>Martes 27: 10 AM y 7 PM CDMX · TikTok · 'Hipnosis para eliminar bloqueos con el dinero'</t>
+          <t>Martes 27: 10 AM y 7 PM CDMX · ZOOM privado (solo registrados) · 'LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO'</t>
         </is>
       </c>
       <c r="E3" s="4" t="inlineStr">
@@ -814,20 +821,20 @@
 0:09–0:30 Hoy hackeo mi miedo a brillar. Hoy hackeo el programa de «esto no es para mí». Hoy hackeo mis memorias de fracaso. Hoy hackeo mi memoria celular y mi subconsciente. Hoy activo mi frecuencia de éxito. [pausa 1.5 s entre cada frase]
 0:30–0:38 Hoy instalo una nueva instrucción: termino lo que empiezo. Me permito avanzar. Me permito ser vista.
 0:38–0:48 Frase clave, 3 veces (pausa 1.5 s entre cada una): El éxito es seguro para mí. El éxito es seguro para mí. El éxito es seguro para mí.
-0:48–0:55 Comenta HIPNOSIS y te mando el link del LIVE gratis de este martes.
+0:48–0:55 El martes hay LIVE gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.
 0:55–1:00 Lo que no se activa, no cambia. Mabel, arroba mabradiante, Método BNQ™.</t>
         </is>
       </c>
       <c r="H2" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: AUDIO ROBÓTICO DEL ÉXITO: ESCÚCHALO 3 VECES (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «EL ÉXITO ES SEGURO PARA MÍ.» parpadea 3 veces. Final: «HIPNOSIS» + @mabradiante · Método BNQ™.</t>
+          <t>0–3 s: AUDIO ROBÓTICO DEL ÉXITO: ESCÚCHALO 3 VECES (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «EL ÉXITO ES SEGURO PARA MÍ.» parpadea 3 veces. Final: «REGÍSTRATE GRATIS · LINK EN MI PERFIL» + @mabradiante · Método BNQ™.</t>
         </is>
       </c>
       <c r="I2" s="4" t="inlineStr">
         <is>
           <t>Tu Activación del Éxito de hoy 🤖✨ Escúchala 3 veces y repite cada decreto conmigo.
 Guárdala para mañana: la repetición es la que instala.
-Comenta HIPNOSIS y te mando el link del LIVE gratis de este martes.</t>
+El martes hay LIVE gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="J2" s="4" t="inlineStr">
@@ -889,25 +896,25 @@
 0:40–0:50 DATO: La Asociación Americana de Psicología describe la hipnosis como un estado de atención enfocada. No te duermes y no pierdes el control: tú decides.
 0:50–0:58 [TU HISTORIA: 1 frase sobre por qué decidiste hacer esta hipnosis gratis y en vivo.]
 0:58–1:10 HACKEO: Repite conmigo 3 veces: mi bloqueo es un programa y hoy lo empiezo a hackear. Mi bloqueo es un programa y hoy lo empiezo a hackear. Mi bloqueo es un programa y hoy lo empiezo a hackear.
-1:10–1:22 INVITACIÓN: «Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero». Martes 27 de octubre, 10 de la mañana y 7 de la noche, hora de la Ciudad de México, aquí en TikTok. Entra al grupo de WhatsApp gratis: el link está en mi perfil.
-1:22–1:28 CTA: Comenta HIPNOSIS y te mando el link.</t>
+1:10–1:22 INVITACIÓN: «LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO». Martes 27 de octubre, 10 de la mañana y 7 de la noche, hora de la Ciudad de México, por Zoom, privado: solo para quien se registra.
+1:22–1:28 CTA: Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H3" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: EL MARTES TE HIPNOTIZO GRATIS (EN VIVO). Lista: 1 BIO-HARDWARE · 2 NEURO-SOFTWARE · 3 QUANTUM-ACTIVACIÓN. Ficha final: «LIVE GRATIS · MARTES 27 OCT · 10 AM y 7 PM (CDMX) · TikTok» + «Comenta HIPNOSIS».</t>
+          <t>0–3 s: EL MARTES TE HIPNOTIZO GRATIS (EN VIVO). Lista: 1 BIO-HARDWARE · 2 NEURO-SOFTWARE · 3 QUANTUM-ACTIVACIÓN. Ficha final: «LIVE GRATIS POR ZOOM · MARTES 27 OCT · 10 AM y 7 PM (CDMX)» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I3" s="4" t="inlineStr">
         <is>
           <t>Tu bloqueo con el dinero no es falta de ganas: es un programa 🧠
 El martes 27 te guío en una hipnosis en vivo y gratis, 10 AM y 7 PM (hora CDMX).
-Regístrate en el grupo de WhatsApp: el link está en mi perfil. O comenta HIPNOSIS y te lo mando 👇</t>
+Es por Zoom, privado. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J3" s="4" t="inlineStr">
         <is>
-          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #tiktoklive</t>
+          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #hipnosisguiada</t>
         </is>
       </c>
       <c r="K3" s="4" t="inlineStr">
@@ -964,19 +971,19 @@
 0:42–0:55 DATO: Los investigadores Sendhil Mullainathan y Eldar Shafir, en su libro «Escasez», explican que cuando la mente vive en carencia se enfoca solo en lo urgente y le cuesta pensar a futuro. No es falta de inteligencia: es una mente ocupada sobreviviendo.
 0:55–1:05 [TU HISTORIA: cuál de las 3 era la tuya y cómo te diste cuenta.]
 1:05–1:15 HACKEO: La próxima vez que te paguen, antes de tocar el dinero, repite 3 veces: este dinero es mío y lo sostengo con calma. Este dinero es mío y lo sostengo con calma. Este dinero es mío y lo sostengo con calma.
-1:15–1:25 INVITACIÓN: Y si quieres ir a la raíz, el martes 27 te guío en una hipnosis gratis en vivo, 10 AM y 7 PM, hora CDMX. Comenta HIPNOSIS y te mando el link del grupo.</t>
+1:15–1:25 INVITACIÓN: Y si quieres ir a la raíz, el martes 27 te guío en una hipnosis gratis en vivo, 10 AM y 7 PM, hora CDMX. Es por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H4" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: LO QUE HACES CUANDO TE LLEGA DINERO LO DICE TODO. Lista: 1 LO GASTAS RÁPIDO · 2 LO ESCONDES CON CULPA · 3 LO REGALAS. Dato: «ESCASEZ» · Mullainathan y Shafir. Final: «LIVE GRATIS MARTES 27 · Comenta HIPNOSIS».</t>
+          <t>0–3 s: LO QUE HACES CUANDO TE LLEGA DINERO LO DICE TODO. Lista: 1 LO GASTAS RÁPIDO · 2 LO ESCONDES CON CULPA · 3 LO REGALAS. Dato: «ESCASEZ» · Mullainathan y Shafir. Final: «LIVE GRATIS POR ZOOM · MARTES 27» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I4" s="4" t="inlineStr">
         <is>
           <t>¿Qué haces las primeras 24 horas después de que te pagan? 💸
 1, 2 o 3: dime cuál es la tuya.
-El martes 27 lo trabajamos en una hipnosis en vivo y gratis. Comenta HIPNOSIS y te mando el link 👇</t>
+El martes 27 lo trabajamos en una hipnosis en vivo y gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J4" s="4" t="inlineStr">
@@ -1036,20 +1043,20 @@
 0:09–0:30 Hoy hackeo mi escasez. Hoy hackeo mis pactos de lealtad con la carencia. Hoy hackeo el «no alcanza» que escuché de niña. Hoy hackeo mi memoria celular y mi subconsciente. Hoy activo mi mente millonaria. [pausa 1.5 s entre cada frase]
 0:30–0:38 Hoy instalo: soy capaz de recibir dinero, sostenerlo y multiplicarlo con calma.
 0:38–0:48 Frase clave, 3 veces (pausa 1.5 s entre cada una): Mi mente millonaria está activada. Mi mente millonaria está activada. Mi mente millonaria está activada.
-0:48–0:55 Comenta HIPNOSIS y te mando el link del LIVE gratis de este martes.
+0:48–0:55 El martes hay LIVE gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.
 0:55–1:00 Lo que no se activa, no cambia. Mabel, arroba mabradiante, Método BNQ™.</t>
         </is>
       </c>
       <c r="H5" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: ACTIVACIÓN MILLONARIA: REPITE ESTO 3 VECES (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «MI MENTE MILLONARIA ESTÁ ACTIVADA.» parpadea 3 veces. Final: «HIPNOSIS» + @mabradiante · Método BNQ™.</t>
+          <t>0–3 s: ACTIVACIÓN MILLONARIA: REPITE ESTO 3 VECES (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «MI MENTE MILLONARIA ESTÁ ACTIVADA.» parpadea 3 veces. Final: «REGÍSTRATE GRATIS · LINK EN MI PERFIL» + @mabradiante · Método BNQ™.</t>
         </is>
       </c>
       <c r="I5" s="4" t="inlineStr">
         <is>
           <t>Tu Activación Millonaria de hoy 🤖✨ Escúchala 3 veces y repite cada decreto conmigo.
 Guárdala para mañana: la repetición es la que instala.
-Comenta HIPNOSIS y te mando el link del LIVE gratis de este martes.</t>
+El martes hay LIVE gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="J5" s="4" t="inlineStr">
@@ -1111,20 +1118,20 @@
 0:40–0:52 DATO: El psicólogo Albert Bandura mostró en los años 60 que los niños aprenden imitando lo que ven hacer a los adultos. Con el dinero pasa lo mismo: aprendiste antes de poder elegir.
 0:52–1:00 [TU HISTORIA: el programa de dinero que heredaste de tu familia.]
 1:00–1:12 HACKEO: Repite conmigo 3 veces: honro a mi familia y elijo un camino nuevo con el dinero. Honro a mi familia y elijo un camino nuevo con el dinero. Honro a mi familia y elijo un camino nuevo con el dinero.
-1:12–1:24 INVITACIÓN: El martes 27 hacemos «Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero». 10 AM y 7 PM, hora CDMX, aquí en TikTok. El registro es en el grupo de WhatsApp: el link está en mi perfil.
-1:24–1:28 CTA: Comenta HIPNOSIS y te lo mando.</t>
+1:12–1:24 INVITACIÓN: El martes 27 hacemos «LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO». 10 AM y 7 PM, hora CDMX, por Zoom, privado: solo para quien se registra.
+1:24–1:28 CTA: Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H6" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: ¿Y SI TU BLOQUEO CON EL DINERO NI SIQUIERA ES TUYO? Lista: 1 FRASES · 2 EMOCIONES · 3 PACTOS DE LEALTAD. Dato: Albert Bandura, aprendizaje por imitación. Final: «LIVE GRATIS · MARTES 27 · 10 AM y 7 PM (CDMX) · Comenta HIPNOSIS».</t>
+          <t>0–3 s: ¿Y SI TU BLOQUEO CON EL DINERO NI SIQUIERA ES TUYO? Lista: 1 FRASES · 2 EMOCIONES · 3 PACTOS DE LEALTAD. Dato: Albert Bandura, aprendizaje por imitación. Final: «LIVE GRATIS POR ZOOM · MARTES 27 · 10 AM y 7 PM (CDMX)» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I6" s="4" t="inlineStr">
         <is>
           <t>Tu bloqueo con el dinero puede ser herencia 🧬 Frases, emociones y pactos de lealtad.
 El martes 27 los hackeamos en una hipnosis en vivo y gratis.
-El link del grupo está en mi perfil, o comenta HIPNOSIS y te lo mando 👇</t>
+Es por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J6" s="4" t="inlineStr">
@@ -1184,21 +1191,21 @@
 0:11–0:20 DOLOR: Muchas no se animan por lo que vieron en la tele: el péndulo, la gente haciendo cosas raras. Eso es espectáculo, no hipnosis.
 0:20–0:40 LISTA DE 3 MITOS: 1. «Me voy a dormir»: no, estás despierta y enfocada. 2. «Voy a perder el control»: no, tú decides todo el tiempo. 3. «Es magia»: no, es tu atención trabajando a tu favor.
 0:40–0:53 DATO: En 2016, un equipo de la Universidad de Stanford, con el psiquiatra David Spiegel, vio en resonancias cómo cambia la actividad del cerebro durante la hipnosis, sobre todo en zonas de atención. Lo espiritual lo llama trance; la ciencia, atención enfocada.
-0:53–1:02 CUIDADOS: En el LIVE: lugar cómodo, audífonos y nunca manejando. Es una práctica de bienestar: no sustituye atención médica ni psicológica.
+0:53–1:02 CUIDADOS: En el LIVE por Zoom: lugar cómodo, audífonos, cámara opcional y nunca manejando. Es una práctica de bienestar: no sustituye atención médica ni psicológica.
 1:02–1:12 HACKEO: Haz esta prueba: cierra los ojos, exhala largo una vez y repite 3 veces: estoy a salvo y yo decido. Estoy a salvo y yo decido. Estoy a salvo y yo decido.
-1:12–1:24 INVITACIÓN: Eso fue un minuto. El martes 27 hacemos 20 minutos juntas, gratis y en vivo, 10 AM y 7 PM, hora CDMX. Comenta HIPNOSIS y te mando el link del grupo.</t>
+1:12–1:24 INVITACIÓN: Eso fue un minuto. El martes 27 hacemos 20 minutos juntas, gratis y en vivo, 10 AM y 7 PM, hora CDMX. Es por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H7" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: LA HIPNOSIS NO ES LO QUE TE CONTARON. Mitos tachados: ✗ ME DUERMO · ✗ PIERDO EL CONTROL · ✗ ES MAGIA. Dato: Stanford · David Spiegel, 2016. Aviso: NO MANEJANDO · NO SUSTITUYE ATENCIÓN MÉDICA. Final: «MARTES 27 · Comenta HIPNOSIS».</t>
+          <t>0–3 s: LA HIPNOSIS NO ES LO QUE TE CONTARON. Mitos tachados: ✗ ME DUERMO · ✗ PIERDO EL CONTROL · ✗ ES MAGIA. Dato: Stanford · David Spiegel, 2016. Aviso: NO MANEJANDO · NO SUSTITUYE ATENCIÓN MÉDICA. Final: «MARTES 27 · POR ZOOM» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I7" s="4" t="inlineStr">
         <is>
           <t>3 mitos de la hipnosis que te alejan de probarla 🌀
 En la hipnosis estás despierta y tú decides.
-El martes 27 la hacemos juntas, gratis y en vivo. Comenta HIPNOSIS y te mando el link 👇</t>
+El martes 27 la hacemos juntas, gratis y en vivo. Es por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J7" s="4" t="inlineStr">
@@ -1258,20 +1265,20 @@
 0:09–0:30 Hoy hackeo la culpa de recibir. Hoy hackeo el «primero los demás y al final yo». Hoy hackeo mis memorias de no ser suficiente. Hoy hackeo mi memoria celular y mi subconsciente. Hoy activo mi merecimiento. [pausa 1.5 s entre cada frase]
 0:30–0:38 Hoy instalo: recibo con gratitud, sin culpa y sin pedir perdón.
 0:38–0:48 Frase clave, 3 veces (pausa 1.5 s entre cada una): Merezco recibir. Merezco recibir. Merezco recibir.
-0:48–0:55 Comenta HIPNOSIS y te mando el link del LIVE gratis de este martes.
+0:48–0:55 El martes hay LIVE gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.
 0:55–1:00 Lo que no se activa, no cambia. Mabel, arroba mabradiante, Método BNQ™.</t>
         </is>
       </c>
       <c r="H8" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: ACTIVACIÓN DE MERECIMIENTO: RECIBE SIN CULPA (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «MEREZCO RECIBIR.» parpadea 3 veces. Final: «HIPNOSIS» + @mabradiante · Método BNQ™.</t>
+          <t>0–3 s: ACTIVACIÓN DE MERECIMIENTO: RECIBE SIN CULPA (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «MEREZCO RECIBIR.» parpadea 3 veces. Final: «REGÍSTRATE GRATIS · LINK EN MI PERFIL» + @mabradiante · Método BNQ™.</t>
         </is>
       </c>
       <c r="I8" s="4" t="inlineStr">
         <is>
           <t>Tu Activación de Merecimiento de hoy 🤖✨ Escúchala 3 veces y repite cada decreto conmigo.
 Guárdala para mañana: la repetición es la que instala.
-Comenta HIPNOSIS y te mando el link del LIVE gratis de este martes.</t>
+El martes hay LIVE gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="J8" s="4" t="inlineStr">
@@ -1329,23 +1336,23 @@
           <t>0:00–0:06 GANCHO: En 2 días vas a cerrar los ojos conmigo y vas a ver tu programa de dinero de frente.
 0:06–0:12 GUARDAR: Guarda este video: es tu lista para prepararte. Y compártelo con quien quieras que te acompañe.
 0:12–0:22 DOLOR: Llevas años intentando cambiar tu relación con el dinero desde la cabeza. Y la cabeza sola no alcanza: el programa está más abajo.
-0:22–0:42 LISTA DE 3 para el martes: 1. Audífonos y un lugar cómodo, nunca manejando. 2. Una hoja con tu intención: ¿qué quieres soltar con el dinero? 3. Llega puntual: 10 AM o 7 PM, hora CDMX.
+0:22–0:42 LISTA DE 3 para el martes: 1. Audífonos y un lugar cómodo, nunca manejando. 2. Una hoja con tu intención: ¿qué quieres soltar con el dinero? 3. Ten a la mano el link de Zoom que te llega por correo y WhatsApp, y entra puntual: 10 AM o 7 PM, hora CDMX.
 0:42–0:55 DATO: El psicólogo Peter Gollwitzer encontró que cuando escribes tu intención con un «cuándo» y un «dónde», es más probable que la cumplas. Por eso la escribes hoy.
 0:55–1:03 [TU HISTORIA: qué sentiste la primera vez que hiciste una hipnosis.]
 1:03–1:14 HACKEO: Escribe tu intención y léela 3 veces en voz alta: el martes suelto mi programa de escasez. El martes suelto mi programa de escasez. El martes suelto mi programa de escasez.
-1:14–1:26 INVITACIÓN: «Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero», martes 27 de octubre, 10 AM y 7 PM, hora CDMX, en TikTok. El link del grupo está en mi perfil. Comenta HIPNOSIS y te lo mando.</t>
+1:14–1:26 INVITACIÓN: «LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO», martes 27 de octubre, 10 AM y 7 PM, hora CDMX, por Zoom, privado. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H9" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: EN 2 DÍAS HACEMOS ESTO JUNTAS EN VIVO. Checklist: ☐ AUDÍFONOS Y LUGAR CÓMODO · ☐ TU INTENCIÓN ESCRITA · ☐ 10 AM o 7 PM (CDMX). Dato: Peter Gollwitzer. Final: «Comenta HIPNOSIS».</t>
+          <t>0–3 s: EN 2 DÍAS HACEMOS ESTO JUNTAS EN VIVO. Checklist: ☐ AUDÍFONOS Y LUGAR CÓMODO · ☐ TU INTENCIÓN ESCRITA · ☐ LINK DE ZOOM A LA MANO · 10 AM o 7 PM (CDMX). Dato: Peter Gollwitzer. Final: «REGÍSTRATE GRATIS · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I9" s="4" t="inlineStr">
         <is>
           <t>Tu lista para el martes ✅ Audífonos, tu intención escrita y llegar puntual.
 Hipnosis gratis y en vivo: martes 27, 10 AM y 7 PM (CDMX).
-El link del grupo de WhatsApp está en mi perfil. Comenta HIPNOSIS y te lo mando 👇</t>
+Es por Zoom, privado. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J9" s="4" t="inlineStr">
@@ -1407,19 +1414,19 @@
 0:40–0:53 DATO: En un estudio de 2005 de David Creswell, publicado en Psychological Science, las personas que repasaron sus valores antes de una prueba estresante mostraron una respuesta de estrés más baja. Lo que te dices antes importa.
 0:53–1:01 [TU HISTORIA: cuándo te dabas cuenta de que tu cuerpo reaccionaba así con el dinero.]
 1:01–1:14 HACKEO: Antes de abrir la app: mano en el pecho, exhala largo una vez y repite 3 veces: puedo ver mi dinero y estoy a salvo. Puedo ver mi dinero y estoy a salvo. Puedo ver mi dinero y estoy a salvo.
-1:14–1:26 INVITACIÓN: El martes 27 vamos a la raíz de esa alarma en una hipnosis gratis en vivo, 10 AM y 7 PM, hora CDMX. El link está en mi perfil. Comenta HIPNOSIS.</t>
+1:14–1:26 INVITACIÓN: El martes 27 vamos a la raíz de esa alarma en una hipnosis gratis en vivo, 10 AM y 7 PM, hora CDMX, por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H10" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: SI SE TE APRIETA EL ESTÓMAGO AL VER TU CUENTA, MIRA ESTO. Lista: 1 EVITAS VER TU SALDO · 2 NUDO AL PAGAR · 3 PELEAS POR DINERO. Dato: Creswell, 2005. Final: «LIVE GRATIS MARTES 27 · Comenta HIPNOSIS».</t>
+          <t>0–3 s: SI SE TE APRIETA EL ESTÓMAGO AL VER TU CUENTA, MIRA ESTO. Lista: 1 EVITAS VER TU SALDO · 2 NUDO AL PAGAR · 3 PELEAS POR DINERO. Dato: Creswell, 2005. Final: «LIVE GRATIS POR ZOOM · MARTES 27» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I10" s="4" t="inlineStr">
         <is>
           <t>¿Te da miedo abrir la app del banco? 😬 No es debilidad: es tu cuerpo en modo alarma.
 Usa este hackeo antes de ver tu cuenta.
-El martes lo trabajamos a fondo en una hipnosis gratis en vivo. Comenta HIPNOSIS 👇</t>
+El martes lo trabajamos a fondo en una hipnosis gratis en vivo. Es por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J10" s="4" t="inlineStr">
@@ -1479,20 +1486,20 @@
 0:09–0:30 Hoy hackeo mi lunes de escasez. Hoy hackeo el miedo a que no alcance. Hoy hackeo la prisa y la carencia. Hoy hackeo mi memoria celular y mi subconsciente. Hoy activo mi frecuencia de abundancia. [pausa 1.5 s entre cada frase]
 0:30–0:38 Hoy instalo: la abundancia me encuentra en lo que hago, en lo que soy y en lo que recibo.
 0:38–0:48 Frase clave, 3 veces (pausa 1.5 s entre cada una): Soy abundancia en movimiento. Soy abundancia en movimiento. Soy abundancia en movimiento.
-0:48–0:55 Mañana es el LIVE gratis. Comenta HIPNOSIS y te mando el link.
+0:48–0:55 Mañana es el LIVE gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.
 0:55–1:00 Lo que no se activa, no cambia. Mabel, arroba mabradiante, Método BNQ™.</t>
         </is>
       </c>
       <c r="H11" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: ACTIVACIÓN DE ABUNDANCIA: EMPIEZA LA SEMANA ASÍ (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «SOY ABUNDANCIA EN MOVIMIENTO.» parpadea 3 veces. Final: «HIPNOSIS» + @mabradiante · Método BNQ™.</t>
+          <t>0–3 s: ACTIVACIÓN DE ABUNDANCIA: EMPIEZA LA SEMANA ASÍ (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «SOY ABUNDANCIA EN MOVIMIENTO.» parpadea 3 veces. Final: «REGÍSTRATE GRATIS · LINK EN MI PERFIL» + @mabradiante · Método BNQ™.</t>
         </is>
       </c>
       <c r="I11" s="4" t="inlineStr">
         <is>
           <t>Tu Activación de Abundancia de hoy 🤖✨ Escúchala 3 veces y repite cada decreto conmigo.
 Guárdala para mañana: la repetición es la que instala.
-Mañana es el LIVE gratis. Comenta HIPNOSIS y te mando el link.</t>
+Mañana es el LIVE gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="J11" s="4" t="inlineStr">
@@ -1554,25 +1561,25 @@
 0:40–0:52 DATO: La Clínica Mayo describe la hipnosis como un estado de atención y concentración elevadas. Por eso funciona como puerta: tu mente se enfoca en una sola instrucción.
 0:52–1:00 [TU HISTORIA: 1 frase de lo que te gustaría que sintieran mañana.]
 1:00–1:12 HACKEO: Hoy en la noche repite 3 veces antes de dormir: mañana me doy permiso de cambiar. Mañana me doy permiso de cambiar. Mañana me doy permiso de cambiar.
-1:12–1:24 INVITACIÓN: «Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero». Mañana martes 27, 10 de la mañana y 7 de la noche, hora CDMX, aquí en TikTok. El link del grupo está en mi perfil.
-1:24–1:28 CTA: Comenta HIPNOSIS y te lo mando.</t>
+1:12–1:24 INVITACIÓN: «LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO». Mañana martes 27, 10 de la mañana y 7 de la noche, hora CDMX, por Zoom, privado: solo para quien se registra.
+1:24–1:28 CTA: Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H12" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: MAÑANA TE HIPNOTIZO EN VIVO (Y ES GRATIS). Lista: 1 POR QUÉ SE BLOQUEA · 2 AUTOHIPNOSIS 20 MIN · 3 TU NUEVA INSTRUCCIÓN. Dato: Clínica Mayo. Ficha final: «MAÑANA · MARTES 27 · 10 AM y 7 PM (CDMX) · TikTok LIVE · Comenta HIPNOSIS».</t>
+          <t>0–3 s: MAÑANA TE HIPNOTIZO EN VIVO (Y ES GRATIS). Lista: 1 POR QUÉ SE BLOQUEA · 2 AUTOHIPNOSIS 20 MIN · 3 TU NUEVA INSTRUCCIÓN. Dato: Clínica Mayo. Ficha final: «MAÑANA · MARTES 27 · 10 AM y 7 PM (CDMX) · POR ZOOM» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I12" s="4" t="inlineStr">
         <is>
-          <t>Mañana es el día 🌀 Hipnosis en vivo y gratis para eliminar bloqueos con el dinero.
-Martes 27, 10 AM y 7 PM (hora CDMX), en TikTok.
-Entra al grupo de WhatsApp: el link está en mi perfil. O comenta HIPNOSIS y te lo mando 👇</t>
+          <t>Mañana es el día 🌀 LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO.
+Martes 27, 10 AM y 7 PM (hora CDMX), por Zoom privado.
+Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J12" s="4" t="inlineStr">
         <is>
-          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #tiktoklive #subconsciente</t>
+          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #hipnosisguiada #subconsciente</t>
         </is>
       </c>
       <c r="K12" s="4" t="inlineStr">
@@ -1629,19 +1636,19 @@
 0:38–0:52 DATO: En 2013, la revista Science publicó un estudio con agricultores de caña en India: les fue mejor en pruebas mentales después de la cosecha, con dinero, que antes, cuando estaban apretados. La escasez ocupa espacio en la mente.
 0:52–1:00 [TU HISTORIA: cuál de las 3 vivías y en qué momento.]
 1:00–1:12 HACKEO de 1 minuto: exhala largo una vez y repite 3 veces: salgo del modo escasez, mi mente tiene espacio. Salgo del modo escasez, mi mente tiene espacio. Salgo del modo escasez, mi mente tiene espacio.
-1:12–1:24 INVITACIÓN: Mañana lo trabajamos más profundo en la hipnosis gratis en vivo: 10 AM y 7 PM, hora CDMX. Comenta HIPNOSIS y te mando el link.</t>
+1:12–1:24 INVITACIÓN: Mañana lo trabajamos más profundo en la hipnosis gratis en vivo: 10 AM y 7 PM, hora CDMX, por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H13" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: 3 SEÑALES DE QUE TU CEREBRO ESTÁ EN MODO ESCASEZ. Lista: 1 PIENSAS EN DINERO TODO EL DÍA · 2 NO PLANEAS MÁS ALLÁ DE LA QUINCENA · 3 GASTOS PEQUEÑOS = MAL HUMOR. Dato: Science, 2013. Final: «MAÑANA LIVE GRATIS · Comenta HIPNOSIS».</t>
+          <t>0–3 s: 3 SEÑALES DE QUE TU CEREBRO ESTÁ EN MODO ESCASEZ. Lista: 1 PIENSAS EN DINERO TODO EL DÍA · 2 NO PLANEAS MÁS ALLÁ DE LA QUINCENA · 3 GASTOS PEQUEÑOS = MAL HUMOR. Dato: Science, 2013. Final: «MAÑANA LIVE GRATIS POR ZOOM» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I13" s="4" t="inlineStr">
         <is>
           <t>¿Cuántas de estas 3 señales tienes? 🧠
 El modo escasez no es tu personalidad: es un estado del que se sale.
-Mañana lo hackeamos en vivo y gratis. Comenta HIPNOSIS y te mando el link 👇</t>
+Mañana lo hackeamos en vivo y gratis por Zoom. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J13" s="4" t="inlineStr">
@@ -1701,20 +1708,20 @@
 0:09–0:30 Hoy hackeo mis manos cerradas. Hoy hackeo el «yo puedo sola». Hoy hackeo el miedo a deber. Hoy hackeo mi memoria celular y mi subconsciente. Hoy activo mi capacidad de recibir. [pausa 1.5 s entre cada frase]
 0:30–0:38 Hoy instalo: abro mis manos, abro mi cuerpo, abro mi vida para recibir.
 0:38–0:48 Frase clave, 3 veces (pausa 1.5 s entre cada una): Hoy me abro a recibir. Hoy me abro a recibir. Hoy me abro a recibir.
-0:48–0:55 Hoy es el LIVE gratis: 10 AM y 7 PM, hora CDMX. El link está en mi perfil.
+0:48–0:55 Hoy es el LIVE gratis por Zoom: 10 AM y 7 PM, hora CDMX. ¿Aún no te registras? Link en mi perfil y te mando el acceso por correo y WhatsApp.
 0:55–1:00 Lo que no se activa, no cambia. Mabel, arroba mabradiante, Método BNQ™.</t>
         </is>
       </c>
       <c r="H14" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: HOY HAY LIVE: ACTIVACIÓN DE RECIBIR (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «HOY ME ABRO A RECIBIR.» parpadea 3 veces. Final: «HOY 10 AM y 7 PM» + @mabradiante · Método BNQ™. Banda fija arriba toda la pieza: «HOY HAY LIVE · 10 AM y 7 PM (CDMX)».</t>
+          <t>0–3 s: HOY HAY LIVE: ACTIVACIÓN DE RECIBIR (letras grandes, fondo negro con código verde/dorado). Después, cada decreto aparece como subtítulo grande al ritmo de la voz. 0:38–0:48: «HOY ME ABRO A RECIBIR.» parpadea 3 veces. Final: «HOY 10 AM y 7 PM · POR ZOOM» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL» + @mabradiante · Método BNQ™. Banda fija arriba toda la pieza: «HOY HAY LIVE POR ZOOM · 10 AM y 7 PM (CDMX)».</t>
         </is>
       </c>
       <c r="I14" s="4" t="inlineStr">
         <is>
           <t>Tu Activación de Recibir de hoy 🤖✨ Escúchala 3 veces y repite cada decreto conmigo.
 Guárdala para mañana: la repetición es la que instala.
-Hoy es el LIVE gratis: 10 AM y 7 PM, hora CDMX. El link está en mi perfil.</t>
+Hoy es el LIVE gratis por Zoom: 10 AM y 7 PM, hora CDMX. Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="J14" s="4" t="inlineStr">
@@ -1754,7 +1761,7 @@
       </c>
       <c r="D15" s="4" t="inlineStr">
         <is>
-          <t>Clip</t>
+          <t>Clip + registro 7 PM</t>
         </is>
       </c>
       <c r="E15" s="4" t="inlineStr">
@@ -1771,26 +1778,26 @@
         <is>
           <t>0:00–0:05 GANCHO (Mabel a cámara o voz sobre el clip): Esto es lo que hicimos hoy a las 10 de la mañana. Y a las 7 lo repito.
 0:05–0:10 GUARDAR: Guárdalo y compártelo con quien no pudo llegar en la mañana.
-0:10–0:45 CLIP REAL DEL LIVE (35 s): [FRAGMENTO REAL de la autohipnosis de las 10:00, de preferencia la parte del decreto Quantum que se repite 3 veces. Subtitulado. Sin editar lo que dijiste.]
-0:45–0:55 CIERRE: Si lo sentiste aunque sea un poquito, imagina los 20 minutos completos. Hoy a las 7 de la noche, hora CDMX, lo repito en vivo aquí en TikTok.
-0:55–1:00 CTA: El link del grupo está en mi perfil. Te espero a las 7.</t>
+0:10–0:45 CLIP REAL DEL LIVE (35 s): [FRAGMENTO REAL de la grabación de Zoom de las 10:00, solo tu cámara (sin caras ni nombres de participantes), de preferencia la parte del decreto Quantum que se repite 3 veces. Subtitulado. Sin editar lo que dijiste.]
+0:45–0:55 CIERRE: Si lo sentiste aunque sea un poquito, imagina los 20 minutos completos. Hoy a las 7 de la noche, hora CDMX, lo repito en vivo por Zoom, privado: solo entra quien se registra.
+0:55–1:00 CTA: Regístrate gratis para la sesión de las 7 PM: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H15" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: ESTO PASÓ HOY EN LA HIPNOSIS EN VIVO. Subtítulos grandes durante el clip. Banda fija: «HOY 7 PM (CDMX) LA REPITO EN VIVO». Final: «LINK EN MI PERFIL».</t>
+          <t>0–3 s: ESTO PASÓ HOY EN LA HIPNOSIS EN VIVO. Subtítulos grandes durante el clip (solo tu cámara, sin participantes). Banda fija: «HOY 7 PM (CDMX) LA REPITO POR ZOOM». Final: «REGÍSTRATE GRATIS PARA LAS 7 PM · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I15" s="4" t="inlineStr">
         <is>
           <t>Así fue la hipnosis en vivo de esta mañana 🌀
-Si no llegaste, hoy a las 7 PM (hora CDMX) la repito, gratis y en vivo en TikTok.
-El link del grupo está en mi perfil. Te espero 👇</t>
+Si no llegaste, hoy a las 7 PM (hora CDMX) la repito, gratis y por Zoom privado.
+Regístrate gratis para la sesión de las 7 PM: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J15" s="4" t="inlineStr">
         <is>
-          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #tiktoklive</t>
+          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #hipnosisguiada</t>
         </is>
       </c>
       <c r="K15" s="4" t="inlineStr">
@@ -1913,25 +1920,25 @@
       </c>
       <c r="G17" s="4" t="inlineStr">
         <is>
-          <t>0:00–0:05 GANCHO: Esto es lo que escribieron ayer en el chat después de la hipnosis.
+          <t>0:00–0:05 GANCHO: Esto es lo que escribieron ayer en el chat de Zoom después de la hipnosis.
 0:05–0:10 GUARDAR: Guárdalo y compártelo con quien se lo perdió.
-0:10–0:30 REACCIONES REALES: [3 comentarios REALES del chat del LIVE, leídos en voz alta o en pantalla, CON PERMISO de quien los escribió. No se inventan ni se editan.]
+0:10–0:30 REACCIONES REALES: [3 mensajes REALES del chat de Zoom del LIVE, leídos en voz alta o en pantalla, CON PERMISO de quien los escribió. No se inventan ni se editan.]
 0:30–0:50 CLIP REAL DEL LIVE (20 s): [FRAGMENTO REAL de la autohipnosis, parte Bio-Hardware: soltar la alarma del cuerpo.]
-0:50–1:02 LISTA DE 3: Si te lo perdiste: 1. La repetición está en el grupo de WhatsApp. 2. Hazla con audífonos y nunca manejando. 3. El martes 3 de noviembre la repito en vivo, 10 AM y 7 PM, hora CDMX.
+0:50–1:02 LISTA DE 3: Si te lo perdiste: 1. La repetición está en el grupo de WhatsApp. 2. Hazla con audífonos y nunca manejando. 3. El martes 3 de noviembre la repito en vivo por Zoom, 10 AM y 7 PM, hora CDMX.
 1:02–1:08 [TU HISTORIA: 1 frase de lo que sentiste tú al ver esas reacciones.]
-1:08–1:15 CTA: El link del grupo está en mi perfil. Comenta HIPNOSIS y te lo mando.</t>
+1:08–1:15 CTA: Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H17" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: LO QUE SINTIERON EN LA HIPNOSIS EN VIVO. Capturas reales del chat (con permiso, nombres ocultos si lo piden). Lista: 1 REPETICIÓN EN EL GRUPO · 2 CON AUDÍFONOS · 3 MARTES 3 NOV OTRA VEZ. Final: «Comenta HIPNOSIS».</t>
+          <t>0–3 s: LO QUE SINTIERON EN LA HIPNOSIS EN VIVO. Capturas reales del chat de Zoom (con permiso, nombres ocultos si lo piden). Lista: 1 REPETICIÓN EN EL GRUPO · 2 CON AUDÍFONOS · 3 MARTES 3 NOV OTRA VEZ POR ZOOM. Final: «REGÍSTRATE GRATIS · LINK EN MI PERFIL».</t>
         </is>
       </c>
       <c r="I17" s="4" t="inlineStr">
         <is>
           <t>Gracias a todas las que llegaron ayer 💛 Esto escribieron después de la hipnosis.
-Si te la perdiste, la repetición está en el grupo de WhatsApp y el martes 3 la repito en vivo.
-El link está en mi perfil. Comenta HIPNOSIS y te lo mando 👇</t>
+Si te la perdiste, la repetición está en el grupo de WhatsApp y el martes 3 la repito en vivo por Zoom.
+Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J17" s="4" t="inlineStr">
@@ -2435,29 +2442,29 @@
           <t>0:00–0:05 GANCHO: Si te perdiste la hipnosis del martes, te doy otra oportunidad.
 0:05–0:11 GUARDAR: Guarda este video para la fecha y compártelo con quien te dijo «la próxima sí voy».
 0:11–0:22 DOLOR: Te enteraste tarde, estabas trabajando o se te olvidó. No pasa nada. Lo importante no es llegar a la primera, es no quedarte con el programa de siempre.
-0:22–0:40 LISTA DE 3: El martes 3: 1. Repetimos la autohipnosis Bio-Hardware, Neuro-Software y Quantum-Activación. 2. Respondo tus preguntas en vivo. 3. Instalas tu nueva instrucción con el decreto.
+0:22–0:40 LISTA DE 3: El martes 3: 1. Repetimos la autohipnosis Bio-Hardware, Neuro-Software y Quantum-Activación. 2. Respondo tus preguntas en vivo, por el chat de Zoom. 3. Instalas tu nueva instrucción con el decreto.
 0:40–0:50 DATO: Como lo describe la Asociación Americana de Psicología, la hipnosis es atención enfocada: estás despierta y tú decides todo el tiempo.
-0:50–1:00 REACCIONES: [1 o 2 reacciones REALES del chat del LIVE 1, con permiso.]
+0:50–1:00 REACCIONES: [1 o 2 reacciones REALES del chat de Zoom del LIVE 1, con permiso.]
 1:00–1:11 HACKEO: Repite conmigo 3 veces: esta vez sí me elijo. Esta vez sí me elijo. Esta vez sí me elijo.
-1:11–1:23 INVITACIÓN: «Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero», martes 3 de noviembre, 10 AM y 7 PM, hora CDMX, en TikTok. El link del grupo está en mi perfil.
-1:23–1:27 CTA: Comenta HIPNOSIS y te lo mando.</t>
+1:11–1:23 INVITACIÓN: «LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO», martes 3 de noviembre, 10 AM y 7 PM, hora CDMX, por Zoom, privado: solo para quien se registra.
+1:23–1:27 CTA: Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H24" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: EL MARTES 3 REPITO LA HIPNOSIS EN VIVO. Lista: 1 AUTOHIPNOSIS BNQ™ · 2 PREGUNTAS EN VIVO · 3 TU DECRETO. Reacciones reales (con permiso). Ficha final: «LIVE GRATIS · MARTES 3 NOV · 10 AM y 7 PM (CDMX) · Comenta HIPNOSIS». Nota chica: «hora de la Ciudad de México».</t>
+          <t>0–3 s: EL MARTES 3 REPITO LA HIPNOSIS EN VIVO. Lista: 1 AUTOHIPNOSIS BNQ™ · 2 PREGUNTAS EN EL CHAT DE ZOOM · 3 TU DECRETO. Reacciones reales (con permiso). Ficha final: «LIVE GRATIS POR ZOOM · MARTES 3 NOV · 10 AM y 7 PM (CDMX)» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL». Nota chica: «hora de la Ciudad de México».</t>
         </is>
       </c>
       <c r="I24" s="4" t="inlineStr">
         <is>
           <t>¿Te perdiste la hipnosis en vivo? 🌀 La repito el martes 3 de noviembre, gratis.
-10 AM y 7 PM, hora CDMX, en TikTok.
-El link del grupo está en mi perfil. Comenta HIPNOSIS y te lo mando 👇</t>
+10 AM y 7 PM, hora CDMX, por Zoom privado.
+Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J24" s="4" t="inlineStr">
         <is>
-          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #tiktoklive</t>
+          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #hipnosisguiada</t>
         </is>
       </c>
       <c r="K24" s="4" t="inlineStr">
@@ -2881,29 +2888,29 @@
           <t>0:00–0:05 GANCHO: Este martes te vuelvo a guiar en una hipnosis en vivo, y esta vez no te la pierdes.
 0:05–0:11 GUARDAR: Guarda este video como recordatorio y compártelo con quien quieras que vaya contigo.
 0:11–0:20 DOLOR: Esta semana honraste a tu familia. El martes sueltas lo que heredaste con el dinero y no te toca cargar.
-0:20–0:38 LISTA DE 3 para estar lista: 1. Entra hoy al grupo de WhatsApp. 2. Elige tu horario: 10 AM o 7 PM, hora CDMX. 3. Audífonos, lugar cómodo y nunca manejando.
+0:20–0:38 LISTA DE 3 para estar lista: 1. Regístrate hoy (link en mi perfil) y entra a la comunidad de WhatsApp. 2. Elige tu horario: 10 AM o 7 PM, hora CDMX. 3. Audífonos, lugar cómodo y nunca manejando.
 0:38–0:50 DATO: La Clínica Mayo describe la hipnosis como un estado de atención y concentración elevadas. Es una práctica de bienestar: no sustituye atención médica ni psicológica.
 0:50–0:58 [TU HISTORIA: 1 frase de lo que más te movió del LIVE pasado.]
 0:58–1:09 HACKEO: Repite 3 veces: el martes me doy una hora para mí. El martes me doy una hora para mí. El martes me doy una hora para mí.
-1:09–1:21 INVITACIÓN: «Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero», martes 3 de noviembre, 10 AM y 7 PM, hora CDMX, en TikTok. El link del grupo está en mi perfil.
-1:21–1:25 CTA: Comenta HIPNOSIS y te lo mando.</t>
+1:09–1:21 INVITACIÓN: «LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO», martes 3 de noviembre, 10 AM y 7 PM, hora CDMX, por Zoom, privado: solo para quien se registra.
+1:21–1:25 CTA: Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp.</t>
         </is>
       </c>
       <c r="H30" s="4" t="inlineStr">
         <is>
-          <t>0–3 s: ESTE MARTES, OTRA VEZ EN VIVO Y GRATIS. Checklist: ☐ ENTRA AL GRUPO · ☐ 10 AM o 7 PM (CDMX) · ☐ AUDÍFONOS. Ficha final: «LIVE GRATIS · MARTES 3 NOV · TikTok · Comenta HIPNOSIS». Nota chica: «hora de la Ciudad de México».</t>
+          <t>0–3 s: ESTE MARTES, OTRA VEZ EN VIVO Y GRATIS. Checklist: ☐ REGÍSTRATE · ☐ 10 AM o 7 PM (CDMX) · ☐ AUDÍFONOS. Ficha final: «LIVE GRATIS POR ZOOM · MARTES 3 NOV» + «REGÍSTRATE GRATIS · LINK EN MI PERFIL». Nota chica: «hora de la Ciudad de México».</t>
         </is>
       </c>
       <c r="I30" s="4" t="inlineStr">
         <is>
           <t>Este martes 3 de noviembre repetimos la hipnosis en vivo y gratis 🌀
-10 AM y 7 PM, hora CDMX, en TikTok.
-Entra al grupo de WhatsApp: el link está en mi perfil. O comenta HIPNOSIS y te lo mando 👇</t>
+10 AM y 7 PM, hora CDMX, por Zoom privado.
+Regístrate gratis: link en mi perfil y te mando el acceso por correo y WhatsApp 👇</t>
         </is>
       </c>
       <c r="J30" s="4" t="inlineStr">
         <is>
-          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #tiktoklive</t>
+          <t>#hipnosis #autohipnosis #hackeatumente #reprogramacionmental #bloqueosconeldinero #abundancia #mabradiante #metodoBNQ #livegratis #hipnosisguiada</t>
         </is>
       </c>
       <c r="K30" s="4" t="inlineStr">
@@ -3074,8 +3081,8 @@
 Te digo lo que nadie te dijo: el dinero no se te va. El dinero va hacia donde está tu programa. Si tu programa dice "el dinero es peligro", tu cuerpo lo va a sacar de tu vida rápido, para estar a salvo. Si tu programa dice "recibir es traicionar a los míos", lo vas a regalar. No es mala suerte. Es lealtad a una instrucción vieja.
 Y la buena noticia es que una instrucción vieja se puede cambiar por una nueva. No de un día para otro, ni por arte de magia. Con ritual, con experiencia, con comprensión y con práctica. Un pago a la vez.
 [15:15–17:00] CTA FINAL: EL LIVE DEL MARTES Y LAS ACTIVACIONES ROBÓTICAS
-Y ahora la invitación. Este martes 27 de octubre voy a hacer un LIVE gratis en TikTok: "Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero". Lo hago dos veces para que te acomode el horario: a las 10 de la mañana y a las 7 de la noche, hora de Ciudad de México. Vamos a hacer una hipnosis guiada, en vivo, para trabajar las tres capas: lo que está grabado en tu cuerpo, los programas que heredaste y la nueva identidad que eliges.
-Para entrar, únete al grupo de WhatsApp. Ahí te mando el recordatorio y el link del LIVE. El link del grupo está en la descripción y en mi Linktree: linktr.ee/mabradiante. Y comenta HIPNOSIS para saber que vas.
+Y ahora la invitación. Este martes 27 de octubre voy a hacer un LIVE gratis por Zoom, privado, solo para quien se registra: "LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO". Lo hago dos veces para que te acomode el horario: a las 10 de la mañana y a las 7 de la noche, hora de Ciudad de México. Vamos a hacer una hipnosis guiada, en vivo, para trabajar las tres capas: lo que está grabado en tu cuerpo, los programas que heredaste y la nueva identidad que eliges.
+Para entrar, regístrate gratis con tu nombre, tu correo y tu país: es el primer botón de mi Linktree, linktr.ee/mabradiante, y también está en www.mabradiante.com. Al registrarte entras a mi comunidad de WhatsApp y te mando el link de Zoom por correo y por WhatsApp. El link de registro está en la descripción.
 Y si quieres empezar desde hoy, antes del martes, ahí mismo están las Activaciones Robóticas Millonarias: diez audios de menos de un minuto, para ponerlos justo antes de cobrar, pagar o vender. 500 pesos. El link está en la descripción y en mi perfil.
 Guarda este episodio, compártelo con esa amiga a la que el dinero también se le va, y nos vemos el martes en vivo. Lo que no se activa, no cambia. Soy Mabel, @mabradiante, Método BNQ™.</t>
         </is>
@@ -3083,11 +3090,10 @@
       <c r="G2" s="4" t="inlineStr">
         <is>
           <t>¿Te pagan y en tres días ya no tienes nada? No eres mala con el dinero: tienes un programa de escasez. En este episodio te explico las 3 señales, lo que encontró un estudio publicado en Science (2013) sobre cómo la escasez ocupa tu mente, las 3 capas del Método BNQ™ y un hackeo de 1 minuto para hacer conmigo antes de pagar, cobrar o vender.
-🔴 LIVE GRATIS EN TIKTOK · MARTES 27 DE OCTUBRE
-«Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero»
-⏰ 10:00 AM y 7:00 PM (hora CDMX) · @mabradiante
-👉 Regístrate en el grupo de WhatsApp: https://linktr.ee/mabradiante
-Comenta HIPNOSIS si vas.
+🔴 LIVE GRATIS POR ZOOM (privado, solo para registrados) · MARTES 27 DE OCTUBRE
+«LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO»
+⏰ 10:00 AM y 7:00 PM (hora CDMX)
+👉 Regístrate gratis (nombre, correo y país): botón 1 de https://linktr.ee/mabradiante o en www.mabradiante.com. Entras a la comunidad de WhatsApp y te mando el link de Zoom por correo y por WhatsApp.
 💰 ACTIVACIONES ROBÓTICAS MILLONARIAS · $500 MXN
 10 audios de menos de 1 minuto para hackear tu programa de escasez justo antes de cobrar, pagar o vender. Tu interruptor.
 👉 https://hotmart.com/es/marketplace/productos/activaciones-roboticas-millonarias-10-audios-para-recibir-dinero-con-facilidad/Q108030809L
@@ -3230,7 +3236,7 @@
 Y tu tarea esta semana: cada vez que sientas culpa por recibir, pon la mano en el pecho y di una sola vez: "Yo puedo pertenecer y recibir."
 [17:00–18:15] CTA FINAL: ACTIVACIONES ROBÓTICAS Y EL SIGUIENTE LIVE
 Si quieres hacer esto en el momento exacto en que se activa el pacto, ahí están las Activaciones Robóticas Millonarias: diez audios de menos de un minuto para hackear tu programa de escasez justo antes de cobrar, pagar o vender. Las pones, cambias tu estado y decides desde ese otro lugar. 500 pesos, y el link está en la descripción y en mi perfil. Comenta PACTO si este episodio te movió algo.
-Y si no llegaste al LIVE, el martes 3 de noviembre lo repito: activación en tiempo real gratis, hipnosis para eliminar bloqueos con el dinero, a las 10 de la mañana y a las 7 de la noche, hora de Ciudad de México, en TikTok. Únete al grupo de WhatsApp desde el link de la descripción o en linktr.ee/mabradiante.
+Y si no llegaste al LIVE, el martes 3 de noviembre lo repito: LIVE gratis, Hipnosis para hackear bloqueos con el dinero, a las 10 de la mañana y a las 7 de la noche, hora de Ciudad de México, por Zoom, privado para quien se registra. Regístrate gratis desde el link de la descripción o en linktr.ee/mabradiante y te mando el acceso por correo y WhatsApp.
 Guarda este episodio, compártelo con alguien de tu familia y nos escuchamos el domingo, Día de Muertos, con una activación para honrar a tus ancestros. Lo que no se activa, no cambia. Soy Mabel, @mabradiante, Método BNQ™.</t>
         </is>
       </c>
@@ -3241,9 +3247,9 @@
 10 audios de menos de 1 minuto para hackear tu programa de escasez justo antes de cobrar, pagar o vender. Tu interruptor.
 👉 https://hotmart.com/es/marketplace/productos/activaciones-roboticas-millonarias-10-audios-para-recibir-dinero-con-facilidad/Q108030809L
 👉 Todos mis links: https://linktr.ee/mabradiante · www.mabradiante.com
-🔴 ¿No llegaste al LIVE? Lo repito GRATIS en TikTok el MARTES 3 DE NOVIEMBRE
-«Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero»
-⏰ 10:00 AM y 7:00 PM (hora CDMX) · Grupo de WhatsApp: https://linktr.ee/mabradiante
+🔴 ¿No llegaste al LIVE? Lo repito GRATIS por ZOOM (privado, solo para registrados) el MARTES 3 DE NOVIEMBRE
+«LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO»
+⏰ 10:00 AM y 7:00 PM (hora CDMX) · Regístrate gratis: https://linktr.ee/mabradiante (te mando el acceso por correo y WhatsApp)
 Comenta PACTO si este episodio te movió algo.
 CAPÍTULOS
 0:00 El dinero se te va por amor
@@ -3384,7 +3390,7 @@
 Cuando tú recibes, tu linaje recibe contigo. Eso, para mí, es lo más espiritual que puedes hacer con tu historia. Y tu tarea de estos días: cada vez que pases frente a tu altar, pon la mano en el pecho y di una vez: "Tomo su fuerza. Les devuelvo su miedo con amor."
 [17:00–18:15] CTA FINAL: ACTIVACIONES ROBÓTICAS Y EL LIVE DEL MARTES
 Si quieres seguir este trabajo en el momento exacto en que la herencia se activa, ahí están las Activaciones Robóticas Millonarias: diez audios de menos de un minuto para hackear tu programa de escasez justo antes de cobrar, pagar o vender. Son tu interruptor: los pones, cambias tu estado y decides desde otro lugar. 500 pesos. El link está en la descripción y en mi perfil. Comenta ANCESTROS si hiciste la activación conmigo.
-Y este martes 3 de noviembre repito el LIVE gratis en TikTok: activación en tiempo real, hipnosis para eliminar bloqueos con el dinero, a las 10 de la mañana y a las 7 de la noche, hora de Ciudad de México. Únete al grupo de WhatsApp desde el link de la descripción o en linktr.ee/mabradiante.
+Y este martes 3 de noviembre repito el LIVE gratis por Zoom, privado para quien se registra: Hipnosis para hackear bloqueos con el dinero, a las 10 de la mañana y a las 7 de la noche, hora de Ciudad de México. Regístrate gratis desde el link de la descripción o en linktr.ee/mabradiante y te mando el acceso por correo y WhatsApp.
 Feliz Día de Muertos. Que tu altar se llene de luz y que tu linaje reciba contigo. Guarda este episodio y compártelo con tu familia. Lo que no se activa, no cambia. Soy Mabel, @mabradiante, Método BNQ™.</t>
         </is>
       </c>
@@ -3395,9 +3401,9 @@
 10 audios de menos de 1 minuto para hackear tu programa de escasez justo antes de cobrar, pagar o vender. Tu interruptor.
 👉 https://hotmart.com/es/marketplace/productos/activaciones-roboticas-millonarias-10-audios-para-recibir-dinero-con-facilidad/Q108030809L
 👉 Todos mis links: https://linktr.ee/mabradiante · www.mabradiante.com
-🔴 LIVE GRATIS EN TIKTOK · MARTES 3 DE NOVIEMBRE
-«Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero»
-⏰ 10:00 AM y 7:00 PM (hora CDMX) · Grupo de WhatsApp: https://linktr.ee/mabradiante
+🔴 LIVE GRATIS POR ZOOM (privado, solo para registrados) · MARTES 3 DE NOVIEMBRE
+«LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO»
+⏰ 10:00 AM y 7:00 PM (hora CDMX) · Regístrate gratis: https://linktr.ee/mabradiante (te mando el acceso por correo y WhatsApp)
 Comenta ANCESTROS si hiciste la activación conmigo.
 CAPÍTULOS
 0:00 Lo que heredaste y no va en el altar
@@ -3482,7 +3488,7 @@
       </c>
       <c r="B2" s="4" t="inlineStr">
         <is>
-          <t>Activación en tiempo real GRATIS · Hipnosis para eliminar bloqueos con el dinero</t>
+          <t>LIVE GRATIS · Hipnosis para HACKEAR bloqueos con el DINERO</t>
         </is>
       </c>
     </row>
@@ -3494,7 +3500,7 @@
       </c>
       <c r="B3" s="4" t="inlineStr">
         <is>
-          <t>TikTok LIVE (sin YouTube Live)</t>
+          <t>ZOOM privado, solo para registrados (2 sesiones: 10 AM y 7 PM). Sin transmisión pública en redes ni en YouTube.</t>
         </is>
       </c>
     </row>
@@ -3530,7 +3536,7 @@
       </c>
       <c r="B6" s="4" t="inlineStr">
         <is>
-          <t>Orgánico: grupo de WhatsApp (link en Linktree, botón 1). Anuncios: formulario de registro (capta correo) → pantalla final con el link del grupo.</t>
+          <t>Formulario de Brevo (nombre, correo, país): botón 1 de https://linktr.ee/mabradiante y banner en www.mabradiante.com → entra a la comunidad de WhatsApp (link en el mensaje de éxito) → recibe el link de Zoom por correo (Brevo) y por WhatsApp. Anuncios: formulario nativo (capta correo) → pantalla final con el link de la comunidad; esos correos se suben a Brevo. El regalo (el LIVE gratis) es a cambio del correo y de entrar a la comunidad.</t>
         </is>
       </c>
     </row>
@@ -3542,7 +3548,7 @@
       </c>
       <c r="B7" s="4" t="inlineStr">
         <is>
-          <t>8:00 'hoy' · 9:00 'en 1 hora' · 10:00 'en vivo' · 18:00 'en 1 hora' · 19:00 'en vivo' · 20:05 'el precio del LIVE cierra a las 21:00' · 21:00 cierra $2,500</t>
+          <t>Por correo y WhatsApp, siempre con el link de Zoom: 8:00 'hoy' · 9:00 'en 1 hora' · 9:55 'ya abrimos la sala de Zoom' · 17:00 pieza 'regístrate para las 7 PM' · 18:00 'en 1 hora' · 18:55 'ya abrimos la sala de Zoom' · 20:05 'el precio del LIVE cierra a las 21:00' · 21:00 cierra $2,500</t>
         </is>
       </c>
     </row>
@@ -3554,7 +3560,7 @@
       </c>
       <c r="B8" s="4" t="inlineStr">
         <is>
-          <t>Robóticas $500 · Pack de Autohipnosis BNQ™ (5 audios, se entregan al comprar) $2,500 solo en el LIVE; después $3,000</t>
+          <t>Al terminar: primero Activaciones Robóticas Millonarias, 1 minuto para salir de la escasez ($500). Venta principal: Pack de Hipnosis BNQ™ (5 audios, se entregan al comprar) $2,500 solo durante el LIVE (cierra martes 27 a las 21:00 CDMX); después $3,000.</t>
         </is>
       </c>
     </row>
@@ -3566,7 +3572,7 @@
       </c>
       <c r="B9" s="4" t="inlineStr">
         <is>
-          <t>Bienvenida: saluda por nombre, '¿de qué ciudad me ves?', 'quédate hasta el final'.</t>
+          <t>Bienvenida: saluda por nombre a quien va entrando a Zoom, '¿desde qué ciudad te conectas? Escríbelo en el chat de Zoom', 'quédate hasta el final'.</t>
         </is>
       </c>
     </row>
@@ -3578,7 +3584,7 @@
       </c>
       <c r="B10" s="4" t="inlineStr">
         <is>
-          <t>Cuidados: lugar cómodo, audífonos, no manejando. Práctica de bienestar, no sustituye atención médica ni psicológica. Línea de la Vida 800 911 2000.</t>
+          <t>Cuidados: lugar cómodo, audífonos, micrófono en silencio, cámara opcional (se puede apagar para la hipnosis), nunca manejando. Práctica de bienestar, no sustituye atención médica ni psicológica. Línea de la Vida 800 911 2000.</t>
         </is>
       </c>
     </row>
@@ -3614,7 +3620,7 @@
       </c>
       <c r="B13" s="4" t="inlineStr">
         <is>
-          <t>Preparación: postura, ojos cerrados, intención.</t>
+          <t>Preparación: audífonos puestos, micrófono en silencio, cámara apagada si así está más cómoda, postura, ojos cerrados, intención.</t>
         </is>
       </c>
     </row>
@@ -3626,7 +3632,7 @@
       </c>
       <c r="B14" s="4" t="inlineStr">
         <is>
-          <t>Autohipnosis en vivo: Hipnosis para eliminar bloqueos con el dinero (la grabas en el otro chat).</t>
+          <t>Autohipnosis en vivo: Hipnosis para HACKEAR bloqueos con el DINERO (la grabas en el otro chat). Tú con cámara y buen audio; los participantes en silencio.</t>
         </is>
       </c>
     </row>
@@ -3638,7 +3644,7 @@
       </c>
       <c r="B15" s="4" t="inlineStr">
         <is>
-          <t>'¿Qué sentiste? Escríbelo en una palabra.' Lee comentarios reales.</t>
+          <t>'¿Qué sentiste? Escríbelo en una palabra en el chat de Zoom.' Lee mensajes reales del chat (sin nombres si no dan permiso).</t>
         </is>
       </c>
     </row>
@@ -3650,7 +3656,7 @@
       </c>
       <c r="B16" s="4" t="inlineStr">
         <is>
-          <t>Oferta Robóticas $500: el interruptor diario de 1 minuto. Link en mi perfil.</t>
+          <t>Oferta 1: Activaciones Robóticas Millonarias, 1 minuto para salir de la escasez ($500). El link va en el chat de Zoom y en la comunidad de WhatsApp.</t>
         </is>
       </c>
     </row>
@@ -3662,7 +3668,7 @@
       </c>
       <c r="B17" s="4" t="inlineStr">
         <is>
-          <t>Oferta Pack de Autohipnosis BNQ™: los 5 audios (Dinero, Relaciones tóxicas, Ansiedad y modo supervivencia, Burnout y modo alarma, Despertar y propósito) + Robóticas + comunidad. $2,500 solo hoy, cierra 21:00; después $3,000.</t>
+          <t>Venta principal: Pack de Hipnosis BNQ™: los 5 audios (Dinero, Relaciones tóxicas, Ansiedad y modo supervivencia, Burnout y modo alarma, Despertar y propósito) + Robóticas + comunidad. $2,500 solo durante el LIVE, cierra hoy martes 27 a las 21:00 CDMX; después $3,000. Link de Hotmart en el chat de Zoom y en la comunidad de WhatsApp.</t>
         </is>
       </c>
     </row>
@@ -3674,7 +3680,7 @@
       </c>
       <c r="B18" s="4" t="inlineStr">
         <is>
-          <t>Preguntas reales, sin presión.</t>
+          <t>Preguntas reales por el chat de Zoom (o abriendo micrófono por turnos), sin presión.</t>
         </is>
       </c>
     </row>
@@ -3856,7 +3862,7 @@
       <c r="C7" s="4" t="inlineStr"/>
       <c r="D7" s="4" t="inlineStr">
         <is>
-          <t>Los correos se descargan y se suben a Brevo. Presupuesto: lo decides tú (no se gasta nada sin tu OK).</t>
+          <t>Los correos se descargan y se suben a Brevo (así reciben el link de Zoom por correo). Presupuesto: lo decides tú (no se gasta nada sin tu OK).</t>
         </is>
       </c>
     </row>
@@ -3885,7 +3891,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B9"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="90" customWidth="1" min="1" max="1"/>
@@ -3947,7 +3953,7 @@
     <row r="6">
       <c r="A6" s="4" t="inlineStr">
         <is>
-          <t>Crear el grupo de WhatsApp del LIVE y ponerlo como botón 1 de Linktree</t>
+          <t>Poner el formulario de registro de Brevo como botón 1 de Linktree y el banner en la web (link de la comunidad de WhatsApp en el mensaje de éxito)</t>
         </is>
       </c>
       <c r="B6" s="4" t="inlineStr">
@@ -3989,6 +3995,18 @@
       <c r="B9" s="4" t="inlineStr">
         <is>
           <t>Pendiente</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="4" t="inlineStr">
+        <is>
+          <t>Crear las 2 reuniones de Zoom (10 AM y 7 PM) y pegar el link en los correos del martes y en la comunidad de WhatsApp</t>
+        </is>
+      </c>
+      <c r="B10" s="4" t="inlineStr">
+        <is>
+          <t>Antes del lunes 26</t>
         </is>
       </c>
     </row>
